--- a/Utilities/titles/classification_titles.xlsx
+++ b/Utilities/titles/classification_titles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/f_j_m_m_nijsse_exeter_ac_uk/Documents/Documents/GitHub/FTT_StandAlone/Utilities/titles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="6_{A4F47DB5-C845-42B4-AA09-B0BE68E5142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53404F45-E592-43D5-96B6-64C98F36193F}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="6_{A4F47DB5-C845-42B4-AA09-B0BE68E5142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E8CFB65-D24C-45B1-BAE4-592C52124811}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="2" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="608">
   <si>
     <t>Full name</t>
   </si>
@@ -808,42 +808,12 @@
     <t>4 Coal + CCS</t>
   </si>
   <si>
-    <t>5 IGCC</t>
-  </si>
-  <si>
-    <t>6 IGCC + CCS</t>
-  </si>
-  <si>
     <t>7 CCGT</t>
   </si>
   <si>
     <t>8 CCGT + CCS</t>
   </si>
   <si>
-    <t>9 Solid Biomass</t>
-  </si>
-  <si>
-    <t>10 S Biomass CCS</t>
-  </si>
-  <si>
-    <t>11 BIGCC</t>
-  </si>
-  <si>
-    <t>12 BIGCC + CCS</t>
-  </si>
-  <si>
-    <t>13 Biogas</t>
-  </si>
-  <si>
-    <t>14 Biogas + CCS</t>
-  </si>
-  <si>
-    <t>15 Tidal</t>
-  </si>
-  <si>
-    <t>16 Large Hydro</t>
-  </si>
-  <si>
     <t>17 Onshore</t>
   </si>
   <si>
@@ -856,18 +826,6 @@
     <t>20 CSP</t>
   </si>
   <si>
-    <t>21 Geothermal</t>
-  </si>
-  <si>
-    <t>22 Wave</t>
-  </si>
-  <si>
-    <t>23 Fuel Cells</t>
-  </si>
-  <si>
-    <t>24 CHP</t>
-  </si>
-  <si>
     <t>4 Gas</t>
   </si>
   <si>
@@ -1889,6 +1847,42 @@
   </si>
   <si>
     <t>21 Techs under mandate</t>
+  </si>
+  <si>
+    <t>5 Waste</t>
+  </si>
+  <si>
+    <t>6 Waste + CCS</t>
+  </si>
+  <si>
+    <t>9 OCGT</t>
+  </si>
+  <si>
+    <t>10 OCGT + CCS</t>
+  </si>
+  <si>
+    <t>11 Biomass</t>
+  </si>
+  <si>
+    <t>12 Biomass + CCS</t>
+  </si>
+  <si>
+    <t>13 Large Hydro</t>
+  </si>
+  <si>
+    <t>14 Pumped Hydro</t>
+  </si>
+  <si>
+    <t>15 Geothermal</t>
+  </si>
+  <si>
+    <t>16 Marine</t>
+  </si>
+  <si>
+    <t>21 Fuel cells / Turbine</t>
+  </si>
+  <si>
+    <t>22 Lithium-ion</t>
   </si>
 </sst>
 </file>
@@ -3164,7 +3158,7 @@
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3188,137 +3182,137 @@
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="3" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="3" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="3" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="3" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="3" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="3" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="3" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="G22" s="3"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="3" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="G23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="3" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>11</v>
@@ -3328,7 +3322,7 @@
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="3" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>8</v>
@@ -3339,7 +3333,7 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="3" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>9</v>
@@ -3350,7 +3344,7 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="3" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>10</v>
@@ -3364,7 +3358,7 @@
         <v>12</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -4155,7 +4149,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -4187,7 +4181,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -4195,7 +4189,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -4203,7 +4197,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -4211,7 +4205,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -4219,7 +4213,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -4234,7 +4228,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C84BF1-D202-40D0-9C0C-F82CFDCF6C25}">
   <sheetPr codeName="Sheet12"/>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -4282,7 +4276,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>596</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -4290,7 +4284,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>250</v>
+        <v>597</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -4298,7 +4292,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -4306,7 +4300,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -4314,7 +4308,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>598</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -4322,7 +4316,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>599</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -4330,7 +4324,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>255</v>
+        <v>600</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -4338,7 +4332,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -4346,7 +4340,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>257</v>
+        <v>602</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -4354,7 +4348,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>258</v>
+        <v>603</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -4362,7 +4356,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>259</v>
+        <v>604</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -4370,7 +4364,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>260</v>
+        <v>605</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -4378,7 +4372,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -4386,7 +4380,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -4394,7 +4388,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -4402,7 +4396,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -4410,7 +4404,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>265</v>
+        <v>606</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -4418,26 +4412,10 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>266</v>
+        <v>607</v>
       </c>
       <c r="B23">
         <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>267</v>
-      </c>
-      <c r="B24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>268</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -4624,7 +4602,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -4654,7 +4632,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -4662,7 +4640,7 @@
     </row>
     <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -4678,7 +4656,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -4694,7 +4672,7 @@
     </row>
     <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -4710,7 +4688,7 @@
     </row>
     <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -4718,7 +4696,7 @@
     </row>
     <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -4726,7 +4704,7 @@
     </row>
     <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -4734,7 +4712,7 @@
     </row>
     <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -4742,7 +4720,7 @@
     </row>
     <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -4750,7 +4728,7 @@
     </row>
     <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -4758,7 +4736,7 @@
     </row>
     <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -4766,7 +4744,7 @@
     </row>
     <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -4774,7 +4752,7 @@
     </row>
     <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -4782,7 +4760,7 @@
     </row>
     <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -4790,7 +4768,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -4798,7 +4776,7 @@
     </row>
     <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -4806,7 +4784,7 @@
     </row>
     <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -4833,7 +4811,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -4841,7 +4819,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -5066,7 +5044,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -5074,7 +5052,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -5082,7 +5060,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -5090,7 +5068,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -5106,7 +5084,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -5114,7 +5092,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -5138,7 +5116,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -5178,7 +5156,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -5186,7 +5164,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -5194,7 +5172,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -5202,7 +5180,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -5210,7 +5188,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -5218,7 +5196,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -5226,7 +5204,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -5470,106 +5448,106 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="B2" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="C2" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="B3" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="C3" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="B4" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="C4" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="B5" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="C5" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="B6" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="C6" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="B7" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C7" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="B8" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="C8" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="B9" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="C9" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="B10" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="C10" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -7021,7 +6999,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -7029,7 +7007,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -7037,7 +7015,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -7045,7 +7023,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -7053,7 +7031,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -7061,7 +7039,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -7069,7 +7047,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -7077,7 +7055,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -7085,7 +7063,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -7093,7 +7071,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -7124,7 +7102,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -7132,7 +7110,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -7140,7 +7118,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -7148,7 +7126,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -7156,7 +7134,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -7164,7 +7142,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -7172,7 +7150,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -7180,7 +7158,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -7188,7 +7166,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -7196,7 +7174,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -7204,7 +7182,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -7212,7 +7190,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -7220,7 +7198,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -7250,7 +7228,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -7266,7 +7244,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -7282,7 +7260,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -7290,7 +7268,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -7362,7 +7340,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -7393,7 +7371,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -7401,7 +7379,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -7409,7 +7387,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -7417,7 +7395,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -7425,7 +7403,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -7433,7 +7411,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -7441,7 +7419,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -7449,7 +7427,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -7457,7 +7435,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -7465,7 +7443,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -7473,7 +7451,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -7481,7 +7459,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -7489,7 +7467,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -7497,7 +7475,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -7505,7 +7483,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -7513,7 +7491,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -7521,7 +7499,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -7529,7 +7507,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -7537,7 +7515,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -7545,7 +7523,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -7553,7 +7531,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -7561,7 +7539,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -7569,7 +7547,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -7577,7 +7555,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -7585,7 +7563,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -7616,119 +7594,119 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="B6" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="B13" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="B14" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -7736,151 +7714,151 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B18" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="B20" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="B21" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B22" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B23" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B24" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B25" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B26" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="B27" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B30" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="B31" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B32" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="B33" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -7888,298 +7866,298 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="B36" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="B37" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="B60" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="B62" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="B63" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="B64" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B65" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="B66" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B67" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="B68" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="B69" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B70" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="B71" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="B72" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -8235,7 +8213,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -8243,7 +8221,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -8251,7 +8229,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -8259,7 +8237,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -8267,7 +8245,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -8275,7 +8253,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -8283,7 +8261,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -8291,7 +8269,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -8299,7 +8277,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -8307,7 +8285,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -8315,7 +8293,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -8472,7 +8450,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -8560,7 +8538,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -8568,7 +8546,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -8576,7 +8554,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -8632,7 +8610,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -8640,7 +8618,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -8648,7 +8626,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -8656,7 +8634,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -8664,7 +8642,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -8672,7 +8650,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -8680,7 +8658,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -8688,7 +8666,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -8696,7 +8674,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -8704,7 +8682,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="B32">
         <v>31</v>
@@ -8734,7 +8712,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -8742,7 +8720,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -8750,7 +8728,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -8758,7 +8736,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -8766,7 +8744,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -8774,7 +8752,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -8782,7 +8760,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -8790,7 +8768,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -8798,7 +8776,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -8806,7 +8784,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -8814,7 +8792,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -8822,7 +8800,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -8830,7 +8808,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -8838,7 +8816,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -8846,7 +8824,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -8854,7 +8832,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -8862,7 +8840,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -8870,7 +8848,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -8878,7 +8856,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -8886,7 +8864,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -8916,34 +8894,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="B2" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="B3" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="B4" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="B5" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -16869,4 +16847,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{912a5d77-fb98-4eee-af32-1334d8f04a53}" enabled="0" method="" siteId="{912a5d77-fb98-4eee-af32-1334d8f04a53}" removed="1"/>
+</clbl:labelList>
 </file>